--- a/data/ground_truth/TLDN.xlsx
+++ b/data/ground_truth/TLDN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muhammadnajmirahmani/Belajar/ProjectDatasaur/data/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E87AFBCA-AC34-2449-AF30-207EFA6B6B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41042FF-627C-C442-A8A0-AD3AC316938D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29300" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="c1H/Q4ZdR4yLnEJr0IZqFh3FObkfqorOjDyrNKq9VL8="/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -39,12 +36,156 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
   <si>
+    <t>(HANYA YANG BISA DIATRIBUSIKAN KE ENTITAS INDUK SAJA)</t>
+  </si>
+  <si>
+    <t>TLDN</t>
+  </si>
+  <si>
+    <t>DINYATAKAN DALAM RUPIAH</t>
+  </si>
+  <si>
+    <t>kecuali nilai nominal dan data saham</t>
+  </si>
+  <si>
+    <t>Q2 2026</t>
+  </si>
+  <si>
+    <t>Q1 2026</t>
+  </si>
+  <si>
+    <t>Q4 2025</t>
+  </si>
+  <si>
+    <t>Q3 2025</t>
+  </si>
+  <si>
+    <t>Q2 2025</t>
+  </si>
+  <si>
+    <t>Q1 2025</t>
+  </si>
+  <si>
+    <t>TAHUNAN 2024</t>
+  </si>
+  <si>
+    <t>Q3 2024</t>
+  </si>
+  <si>
+    <t>Q2 2024</t>
+  </si>
+  <si>
+    <t>Q1 2024</t>
+  </si>
+  <si>
+    <t>TAHUNAN 2023</t>
+  </si>
+  <si>
+    <t>Q3 2023</t>
+  </si>
+  <si>
+    <t>Q2 2023</t>
+  </si>
+  <si>
+    <t>Q1 2023</t>
+  </si>
+  <si>
+    <t>TAHUNAN 2022</t>
+  </si>
+  <si>
+    <t>Q3 2022</t>
+  </si>
+  <si>
+    <t>Q2 2022</t>
+  </si>
+  <si>
+    <t>Q1 2022</t>
+  </si>
+  <si>
+    <t>TAHUNAN 2021</t>
+  </si>
+  <si>
+    <t>Q3 2021</t>
+  </si>
+  <si>
+    <t>Q2 2021</t>
+  </si>
+  <si>
+    <t>Q1 2021</t>
+  </si>
+  <si>
+    <t>TAHUNAN 2020</t>
+  </si>
+  <si>
+    <t>Q3 2020</t>
+  </si>
+  <si>
+    <t>Q2 2020</t>
+  </si>
+  <si>
+    <t>Q1 2020</t>
+  </si>
+  <si>
+    <t>Aset</t>
+  </si>
+  <si>
+    <t>total aset lancar</t>
+  </si>
+  <si>
+    <t>KAS</t>
+  </si>
+  <si>
+    <t>liabilitas</t>
+  </si>
+  <si>
+    <t>Utang Bank SAJA Jangka Pendek + Panjang jatuh tempo</t>
+  </si>
+  <si>
+    <t>ekuitas</t>
+  </si>
+  <si>
+    <t>laba bersih</t>
+  </si>
+  <si>
+    <t>pendapatan dari kontrak dengan pelanggan</t>
+  </si>
+  <si>
+    <t>kas dari aktivitas operasi</t>
+  </si>
+  <si>
+    <t>total share</t>
+  </si>
+  <si>
+    <t>Harga saham rupiah</t>
+  </si>
+  <si>
+    <t>Book Value per share</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>ROA</t>
+  </si>
+  <si>
+    <t>ROE</t>
+  </si>
+  <si>
+    <t>PBV</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>EPS</t>
+  </si>
+  <si>
+    <t>DER</t>
+  </si>
+  <si>
     <t>Perusahaan</t>
   </si>
   <si>
-    <t>(HANYA YANG BISA DIATRIBUSIKAN KE ENTITAS INDUK SAJA)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lokasi </t>
   </si>
   <si>
@@ -54,9 +195,6 @@
     <t>PT Cipta Davia Mandiri</t>
   </si>
   <si>
-    <t>TLDN</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kutai Timur, Kaltim </t>
   </si>
   <si>
@@ -97,159 +235,19 @@
   </si>
   <si>
     <t>Tanjung Buyu Perkasa Plantation</t>
-  </si>
-  <si>
-    <t>DINYATAKAN DALAM RUPIAH</t>
-  </si>
-  <si>
-    <t>kecuali nilai nominal dan data saham</t>
-  </si>
-  <si>
-    <t>Q2 2026</t>
-  </si>
-  <si>
-    <t>Q1 2026</t>
-  </si>
-  <si>
-    <t>Q4 2025</t>
-  </si>
-  <si>
-    <t>Q3 2025</t>
-  </si>
-  <si>
-    <t>Q2 2025</t>
-  </si>
-  <si>
-    <t>Q1 2025</t>
-  </si>
-  <si>
-    <t>TAHUNAN 2024</t>
-  </si>
-  <si>
-    <t>Q3 2024</t>
-  </si>
-  <si>
-    <t>Q2 2024</t>
-  </si>
-  <si>
-    <t>Q1 2024</t>
-  </si>
-  <si>
-    <t>TAHUNAN 2023</t>
-  </si>
-  <si>
-    <t>Q3 2023</t>
-  </si>
-  <si>
-    <t>Q2 2023</t>
-  </si>
-  <si>
-    <t>Q1 2023</t>
-  </si>
-  <si>
-    <t>TAHUNAN 2022</t>
-  </si>
-  <si>
-    <t>Q3 2022</t>
-  </si>
-  <si>
-    <t>Q2 2022</t>
-  </si>
-  <si>
-    <t>Q1 2022</t>
-  </si>
-  <si>
-    <t>TAHUNAN 2021</t>
-  </si>
-  <si>
-    <t>Q3 2021</t>
-  </si>
-  <si>
-    <t>Q2 2021</t>
-  </si>
-  <si>
-    <t>Q1 2021</t>
-  </si>
-  <si>
-    <t>TAHUNAN 2020</t>
-  </si>
-  <si>
-    <t>Q3 2020</t>
-  </si>
-  <si>
-    <t>Q2 2020</t>
-  </si>
-  <si>
-    <t>Q1 2020</t>
-  </si>
-  <si>
-    <t>Aset</t>
-  </si>
-  <si>
-    <t>total aset lancar</t>
-  </si>
-  <si>
-    <t>KAS</t>
-  </si>
-  <si>
-    <t>liabilitas</t>
-  </si>
-  <si>
-    <t>Utang Bank SAJA Jangka Pendek + Panjang jatuh tempo</t>
-  </si>
-  <si>
-    <t>ekuitas</t>
-  </si>
-  <si>
-    <t>laba bersih</t>
-  </si>
-  <si>
-    <t>pendapatan dari kontrak dengan pelanggan</t>
-  </si>
-  <si>
-    <t>kas dari aktivitas operasi</t>
-  </si>
-  <si>
-    <t>total share</t>
-  </si>
-  <si>
-    <t>Harga saham rupiah</t>
-  </si>
-  <si>
-    <t>Book Value per share</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>ROA</t>
-  </si>
-  <si>
-    <t>ROE</t>
-  </si>
-  <si>
-    <t>PBV</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>EPS</t>
-  </si>
-  <si>
-    <t>DER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,17 +258,25 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -296,10 +302,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -311,12 +318,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -329,8 +331,11 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -556,15 +561,16 @@
     <col min="9" max="9" width="19.5" customWidth="1"/>
     <col min="10" max="10" width="17.5" customWidth="1"/>
     <col min="11" max="11" width="17.1640625" customWidth="1"/>
-    <col min="12" max="27" width="8.6640625" customWidth="1"/>
+    <col min="12" max="18" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="27" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>5</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -591,12 +597,12 @@
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -622,597 +628,755 @@
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="U3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="V3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="W3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="X3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="Y3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="Z3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="AA3" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="7">
+        <v>30</v>
+      </c>
+      <c r="B4" s="13">
         <v>6342799138000</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="13">
         <v>6287074631000</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="13">
         <v>6018032137000</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="13">
         <v>6207108405000</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="13">
         <v>5922715715000</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="13">
         <v>5976239681000</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="13">
         <v>5664445219000</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="13">
+        <v>5488214031000</v>
+      </c>
+      <c r="J4" s="13">
+        <v>5499047458000</v>
+      </c>
+      <c r="K4" s="13">
+        <v>5769720845000</v>
+      </c>
+      <c r="L4" s="13">
+        <v>5423799394000</v>
+      </c>
+      <c r="M4" s="13">
         <v>5436056871000</v>
       </c>
-      <c r="J4" s="7">
+      <c r="N4" s="13">
         <v>5171540190000</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
+      <c r="O4" s="13">
+        <v>5398021853000</v>
+      </c>
+      <c r="P4" s="13">
+        <v>5224551902000</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>5427074583000</v>
+      </c>
+      <c r="R4" s="13">
+        <v>5115271340000</v>
+      </c>
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="7">
+        <v>31</v>
+      </c>
+      <c r="B5" s="13">
         <v>1914357059000</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="13">
         <v>1952459070000</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="13">
         <v>1588829853000</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="13">
         <v>1819609212000</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="13">
         <v>1684520584000</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="13">
         <v>2073151943000</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="13">
         <v>1766579819000</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="13">
+        <v>1607493338000</v>
+      </c>
+      <c r="J5" s="13">
+        <v>1613179856000</v>
+      </c>
+      <c r="K5" s="13">
+        <v>1875022669000</v>
+      </c>
+      <c r="L5" s="13">
+        <v>1613998990000</v>
+      </c>
+      <c r="M5" s="13">
         <v>1702439782000</v>
       </c>
-      <c r="J5" s="7">
+      <c r="N5" s="13">
         <v>1596650258000</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
+      <c r="O5" s="13">
+        <v>1929445126000</v>
+      </c>
+      <c r="P5" s="13">
+        <v>1756866967000</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>1976386640000</v>
+      </c>
+      <c r="R5" s="13">
+        <v>1681968054000</v>
+      </c>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="7">
+        <v>32</v>
+      </c>
+      <c r="B6" s="13">
         <v>258018162000</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="13">
         <v>695168978000</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="13">
         <v>334385754000</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="13">
         <v>453355101000</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="13">
         <v>276683736000</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="13">
         <v>821851671000</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="13">
         <v>486587666000</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="13">
+        <v>386721193000</v>
+      </c>
+      <c r="J6" s="13">
+        <v>359927276000</v>
+      </c>
+      <c r="K6" s="13">
+        <v>727445233000</v>
+      </c>
+      <c r="L6" s="13">
+        <v>583295262000</v>
+      </c>
+      <c r="M6" s="13">
         <v>506251051000</v>
       </c>
-      <c r="J6" s="7">
+      <c r="N6" s="13">
         <v>380517170000</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
+      <c r="O6" s="13">
+        <v>724565113000</v>
+      </c>
+      <c r="P6" s="13">
+        <v>587554526000</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>428262596000</v>
+      </c>
+      <c r="R6" s="13">
+        <v>290672636000</v>
+      </c>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="7">
+        <v>33</v>
+      </c>
+      <c r="B7" s="13">
         <v>2651152175000</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="13">
         <v>2460394233000</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="13">
         <v>2373123326000</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="13">
         <v>2631574846000</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="13">
         <v>2615212576000</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="13">
         <v>2612501553000</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="13">
         <v>2519627219000</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="13">
+        <v>2793022047000</v>
+      </c>
+      <c r="J7" s="13">
+        <v>2928706623000</v>
+      </c>
+      <c r="K7" s="13">
+        <v>3241193629000</v>
+      </c>
+      <c r="L7" s="13">
+        <v>2965522409000</v>
+      </c>
+      <c r="M7" s="13">
         <v>3196613547000</v>
       </c>
-      <c r="J7" s="10">
+      <c r="N7" s="13">
         <v>3102894029000</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
+      <c r="O7" s="13">
+        <v>3165830467000</v>
+      </c>
+      <c r="P7" s="13">
+        <v>3044544460000</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>3304110682000</v>
+      </c>
+      <c r="R7" s="13">
+        <v>3045489535000</v>
+      </c>
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="7">
+        <v>34</v>
+      </c>
+      <c r="B8" s="13">
         <v>124347189000</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="13">
         <v>165863709000</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="13">
         <v>190767674000</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="13">
         <v>141500000000</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="13">
         <v>122902518000</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="13">
         <v>290757191000</v>
       </c>
-      <c r="H8" s="5">
-        <f>20000000000+337603441000</f>
+      <c r="H8" s="13">
         <v>357603441000</v>
       </c>
-      <c r="I8" s="5">
-        <f>441100000000</f>
-        <v>441100000000</v>
-      </c>
-      <c r="J8" s="10">
+      <c r="I8" s="13">
+        <v>525573270000</v>
+      </c>
+      <c r="J8" s="13">
+        <v>531498270000</v>
+      </c>
+      <c r="K8" s="13">
+        <v>378873000000</v>
+      </c>
+      <c r="L8" s="13">
+        <v>443624000000</v>
+      </c>
+      <c r="M8" s="13">
+        <v>504707348000</v>
+      </c>
+      <c r="N8" s="13">
         <v>469775000000</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
+      <c r="O8" s="13">
+        <v>498450000000</v>
+      </c>
+      <c r="P8" s="13">
+        <v>554050000000</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>543650000000</v>
+      </c>
+      <c r="R8" s="13">
+        <v>561750000000</v>
+      </c>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="7">
+        <v>35</v>
+      </c>
+      <c r="B9" s="13">
         <v>3691598827000</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="13">
         <v>3826634977000</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="13">
         <v>3644864762000</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="13">
         <v>3575485566000</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="13">
         <v>3307456949000</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="13">
         <v>3363694421000</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="13">
         <v>3144775624000</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="13">
+        <v>2695153115000</v>
+      </c>
+      <c r="J9" s="13">
+        <v>2570303026000</v>
+      </c>
+      <c r="K9" s="13">
+        <v>2528491061000</v>
+      </c>
+      <c r="L9" s="13">
+        <v>2458241414000</v>
+      </c>
+      <c r="M9" s="13">
         <v>2239409582000</v>
       </c>
-      <c r="J9" s="10">
+      <c r="N9" s="13">
         <v>2068614365000</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
+      <c r="O9" s="13">
+        <v>2232159707000</v>
+      </c>
+      <c r="P9" s="13">
+        <v>2179976035000</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>2122933797000</v>
+      </c>
+      <c r="R9" s="13">
+        <v>2069752193000</v>
+      </c>
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="7">
+        <v>36</v>
+      </c>
+      <c r="B10" s="13">
         <v>543642277000</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="13">
         <v>181770215000</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="13">
         <v>1106606494000</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="13">
         <v>829300009000</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="13">
         <v>561271392000</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="13">
         <v>218918797000</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="13">
         <v>825587405000</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="13">
+        <v>393904832000</v>
+      </c>
+      <c r="J10" s="13">
+        <v>269054743000</v>
+      </c>
+      <c r="K10" s="13">
+        <v>70249647000</v>
+      </c>
+      <c r="L10" s="13">
+        <v>451789538000</v>
+      </c>
+      <c r="M10" s="13">
         <v>234190360000</v>
       </c>
-      <c r="J10" s="10">
+      <c r="N10" s="13">
         <v>63395143000</v>
       </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
+      <c r="O10" s="13">
+        <v>52183672000</v>
+      </c>
+      <c r="P10" s="13">
+        <v>573973852000</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>560468184000</v>
+      </c>
+      <c r="R10" s="13">
+        <v>507129583000</v>
+      </c>
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
     </row>
     <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="7">
-        <v>2968533550000</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1587018948000</v>
-      </c>
-      <c r="D11" s="7">
-        <v>5330133466000</v>
-      </c>
-      <c r="E11" s="7">
-        <v>4028946553000</v>
-      </c>
-      <c r="F11" s="7">
-        <v>2691885302000</v>
-      </c>
-      <c r="G11" s="7">
-        <v>1457165917000</v>
-      </c>
-      <c r="H11" s="7">
+        <v>37</v>
+      </c>
+      <c r="B11" s="13">
+        <v>2714423457000</v>
+      </c>
+      <c r="C11" s="13">
+        <v>1367452843000</v>
+      </c>
+      <c r="D11" s="13">
+        <v>5421391584000</v>
+      </c>
+      <c r="E11" s="13">
+        <v>3813244295000</v>
+      </c>
+      <c r="F11" s="13">
+        <v>2549841179000</v>
+      </c>
+      <c r="G11" s="13">
+        <v>1280624553000</v>
+      </c>
+      <c r="H11" s="13">
         <v>4211481582000</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="13">
+        <v>2868602829000</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1865434549000</v>
+      </c>
+      <c r="K11" s="13">
+        <v>858644407000</v>
+      </c>
+      <c r="L11" s="13">
+        <v>4007082262000</v>
+      </c>
+      <c r="M11" s="13">
         <v>2885430562000</v>
       </c>
-      <c r="J11" s="7">
+      <c r="N11" s="13">
         <v>1915665661000</v>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
+      <c r="O11" s="13">
+        <v>955565876000</v>
+      </c>
+      <c r="P11" s="13">
+        <v>3613176678000</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>2467677554000</v>
+      </c>
+      <c r="R11" s="13">
+        <v>1770137910000</v>
+      </c>
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
     </row>
     <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="7">
+        <v>38</v>
+      </c>
+      <c r="B12" s="13">
         <v>851671746000</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="13">
         <v>545153215000</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="13">
         <v>1544117069000</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="13">
         <v>1670634109000</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="13">
         <v>1199712765000</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="13">
         <v>612102984000</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="13">
         <v>1140257076000</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="13">
+        <v>863545856000</v>
+      </c>
+      <c r="J12" s="13">
+        <v>531522269000</v>
+      </c>
+      <c r="K12" s="13">
+        <v>472816520000</v>
+      </c>
+      <c r="L12" s="13">
+        <v>1313645740000</v>
+      </c>
+      <c r="M12" s="13">
         <v>947753157000</v>
       </c>
-      <c r="J12" s="10">
-        <v>1901117155000</v>
-      </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
+      <c r="N12" s="13">
+        <v>432252797000</v>
+      </c>
+      <c r="O12" s="13">
+        <v>332794438000</v>
+      </c>
+      <c r="P12" s="13">
+        <v>799499935000</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>399402620000</v>
+      </c>
+      <c r="R12" s="13">
+        <v>63324628000</v>
+      </c>
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
     </row>
     <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="7">
+        <v>39</v>
+      </c>
+      <c r="B13" s="13">
         <v>12946530200</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="13">
         <v>12946530200</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="13">
         <v>12946530200</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="13">
         <v>12946530200</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="13">
         <v>12946530200</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="13">
         <v>12946530200</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="13">
         <v>12946530200</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="13">
         <v>12946530200</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="13">
         <v>12946530200</v>
       </c>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
+      <c r="K13" s="13">
+        <v>12946530200</v>
+      </c>
+      <c r="L13" s="13">
+        <v>12946530200</v>
+      </c>
+      <c r="M13" s="13">
+        <v>12946530200</v>
+      </c>
+      <c r="N13" s="13">
+        <v>12946530200</v>
+      </c>
+      <c r="O13" s="13">
+        <v>12946530200</v>
+      </c>
+      <c r="P13" s="13">
+        <v>12946530200</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>12946530200</v>
+      </c>
+      <c r="R13" s="13">
+        <v>12946530200</v>
+      </c>
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
     </row>
     <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B14" s="4">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C14" s="4">
-        <v>472</v>
+        <v>530</v>
       </c>
       <c r="D14" s="4">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="E14" s="4">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="F14" s="4">
         <v>630</v>
       </c>
       <c r="G14" s="4">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="H14" s="5">
         <v>585</v>
@@ -1221,63 +1385,63 @@
         <v>520</v>
       </c>
       <c r="J14" s="5">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K14" s="5">
         <v>444</v>
       </c>
       <c r="L14" s="5">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M14" s="5">
         <v>454</v>
       </c>
       <c r="N14" s="5">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O14" s="5">
         <v>454</v>
       </c>
       <c r="P14" s="5">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="Q14" s="5">
         <v>580</v>
       </c>
       <c r="R14" s="5">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="S14" s="5">
         <v>650</v>
       </c>
       <c r="T14" s="5">
-        <v>725</v>
-      </c>
-      <c r="U14" s="9">
+        <v>665</v>
+      </c>
+      <c r="U14" s="7">
         <v>570</v>
       </c>
-      <c r="V14" s="9">
+      <c r="V14" s="7">
         <v>570</v>
       </c>
       <c r="W14" s="4">
         <v>570</v>
       </c>
-      <c r="X14" s="9">
+      <c r="X14" s="7">
         <v>570</v>
       </c>
-      <c r="Y14" s="9">
+      <c r="Y14" s="7">
         <v>570</v>
       </c>
-      <c r="Z14" s="9">
+      <c r="Z14" s="7">
         <v>1140</v>
       </c>
-      <c r="AA14" s="9">
+      <c r="AA14" s="7">
         <v>1140</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>59</v>
+      <c r="A15" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="B15" s="6">
         <f t="shared" ref="B15:AA15" si="0">B9/B13</f>
@@ -1309,43 +1473,43 @@
       </c>
       <c r="I15" s="6">
         <f t="shared" si="0"/>
-        <v>172.97372712265405</v>
+        <v>208.17570989020672</v>
       </c>
       <c r="J15" s="6">
         <f t="shared" si="0"/>
+        <v>198.53219250977378</v>
+      </c>
+      <c r="K15" s="6">
+        <f t="shared" si="0"/>
+        <v>195.30260401354488</v>
+      </c>
+      <c r="L15" s="6">
+        <f t="shared" si="0"/>
+        <v>189.87646697800156</v>
+      </c>
+      <c r="M15" s="6">
+        <f t="shared" si="0"/>
+        <v>172.97372712265405</v>
+      </c>
+      <c r="N15" s="6">
+        <f t="shared" si="0"/>
         <v>159.78137254103805</v>
       </c>
-      <c r="K15" s="6" t="e">
+      <c r="O15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L15" s="6" t="e">
+        <v>172.41374117367755</v>
+      </c>
+      <c r="P15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M15" s="6" t="e">
+        <v>168.38303401169219</v>
+      </c>
+      <c r="Q15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N15" s="6" t="e">
+        <v>163.97704745631381</v>
+      </c>
+      <c r="R15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O15" s="6" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P15" s="6" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q15" s="6" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R15" s="6" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>159.86925925527134</v>
       </c>
       <c r="S15" s="6" t="e">
         <f t="shared" si="0"/>
@@ -1367,26 +1531,26 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X15" s="12" t="e">
+      <c r="X15" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y15" s="12" t="e">
+      <c r="Y15" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z15" s="12" t="e">
+      <c r="Z15" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA15" s="12" t="e">
+      <c r="AA15" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>60</v>
+      <c r="A16" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="B16" s="6">
         <f t="shared" ref="B16:AA16" si="1">B5-B7</f>
@@ -1418,43 +1582,43 @@
       </c>
       <c r="I16" s="6">
         <f t="shared" si="1"/>
-        <v>-1494173765000</v>
+        <v>-1185528709000</v>
       </c>
       <c r="J16" s="6">
         <f t="shared" si="1"/>
-        <v>-1506243771000</v>
+        <v>-1315526767000</v>
       </c>
       <c r="K16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1366170960000</v>
       </c>
       <c r="L16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1351523419000</v>
       </c>
       <c r="M16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1494173765000</v>
       </c>
       <c r="N16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1506243771000</v>
       </c>
       <c r="O16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1236385341000</v>
       </c>
       <c r="P16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1287677493000</v>
       </c>
       <c r="Q16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1327724042000</v>
       </c>
       <c r="R16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1363521481000</v>
       </c>
       <c r="S16" s="6">
         <f t="shared" si="1"/>
@@ -1476,462 +1640,462 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X16" s="12">
+      <c r="X16" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y16" s="12">
+      <c r="Y16" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="12">
+      <c r="Z16" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="12">
+      <c r="AA16" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="13">
+      <c r="A17" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="10">
         <f t="shared" ref="B17:AA17" si="2">B10/B4</f>
         <v>8.5710151807112139E-2</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="10">
         <f t="shared" si="2"/>
         <v>2.8911731714418708E-2</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="10">
         <f t="shared" si="2"/>
         <v>0.1838817854089502</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="10">
         <f t="shared" si="2"/>
         <v>0.13360488570361934</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="10">
         <f t="shared" si="2"/>
         <v>9.4765884268007625E-2</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="10">
         <f t="shared" si="2"/>
         <v>3.6631528968960041E-2</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="10">
         <f t="shared" si="2"/>
         <v>0.14574903156107299</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="10">
+        <f t="shared" si="2"/>
+        <v>7.1772862679013838E-2</v>
+      </c>
+      <c r="J17" s="10">
+        <f t="shared" si="2"/>
+        <v>4.8927517911957617E-2</v>
+      </c>
+      <c r="K17" s="10">
+        <f t="shared" si="2"/>
+        <v>1.2175571208246212E-2</v>
+      </c>
+      <c r="L17" s="10">
+        <f t="shared" si="2"/>
+        <v>8.3297612094537579E-2</v>
+      </c>
+      <c r="M17" s="10">
         <f t="shared" si="2"/>
         <v>4.30809253025565E-2</v>
       </c>
-      <c r="J17" s="13">
+      <c r="N17" s="10">
         <f t="shared" si="2"/>
         <v>1.2258464726346834E-2</v>
       </c>
-      <c r="K17" s="13" t="e">
+      <c r="O17" s="10">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L17" s="13" t="e">
+        <v>9.667184279922551E-3</v>
+      </c>
+      <c r="P17" s="10">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M17" s="13" t="e">
+        <v>0.10986087663906224</v>
+      </c>
+      <c r="Q17" s="10">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N17" s="13" t="e">
+        <v>0.10327261500249775</v>
+      </c>
+      <c r="R17" s="10">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O17" s="13" t="e">
+        <v>9.9140309338898142E-2</v>
+      </c>
+      <c r="S17" s="10" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P17" s="13" t="e">
+      <c r="T17" s="10" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q17" s="13" t="e">
+      <c r="U17" s="10" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R17" s="13" t="e">
+      <c r="V17" s="10" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S17" s="13" t="e">
+      <c r="W17" s="10" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T17" s="13" t="e">
+      <c r="X17" s="10" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U17" s="13" t="e">
+      <c r="Y17" s="10" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V17" s="13" t="e">
+      <c r="Z17" s="10" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W17" s="13" t="e">
+      <c r="AA17" s="10" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X17" s="13" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y17" s="13" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z17" s="13" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA17" s="13" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="13">
+      <c r="A18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="10">
         <f t="shared" ref="B18:AA18" si="3">B10/B9</f>
         <v>0.14726472254348238</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="10">
         <f t="shared" si="3"/>
         <v>4.7501320636154316E-2</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="10">
         <f t="shared" si="3"/>
         <v>0.3036070104814495</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="10">
         <f t="shared" si="3"/>
         <v>0.23194052771069137</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="10">
         <f t="shared" si="3"/>
         <v>0.16969877481540577</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="10">
         <f t="shared" si="3"/>
         <v>6.5082843326450909E-2</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="10">
         <f t="shared" si="3"/>
         <v>0.26252664854667546</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="10">
+        <f t="shared" si="3"/>
+        <v>0.14615304407297097</v>
+      </c>
+      <c r="J18" s="10">
+        <f t="shared" si="3"/>
+        <v>0.10467821897977254</v>
+      </c>
+      <c r="K18" s="10">
+        <f t="shared" si="3"/>
+        <v>2.7783229327382621E-2</v>
+      </c>
+      <c r="L18" s="10">
+        <f t="shared" si="3"/>
+        <v>0.18378566703294505</v>
+      </c>
+      <c r="M18" s="10">
         <f t="shared" si="3"/>
         <v>0.10457683216254096</v>
       </c>
-      <c r="J18" s="13">
+      <c r="N18" s="10">
         <f t="shared" si="3"/>
         <v>3.0646187164034316E-2</v>
       </c>
-      <c r="K18" s="13" t="e">
+      <c r="O18" s="10">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L18" s="13" t="e">
+        <v>2.3378108580830143E-2</v>
+      </c>
+      <c r="P18" s="10">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M18" s="13" t="e">
+        <v>0.26329365221668594</v>
+      </c>
+      <c r="Q18" s="10">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N18" s="13" t="e">
+        <v>0.2640064352416544</v>
+      </c>
+      <c r="R18" s="10">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O18" s="13" t="e">
+        <v>0.24501946885967135</v>
+      </c>
+      <c r="S18" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P18" s="13" t="e">
+      <c r="T18" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q18" s="13" t="e">
+      <c r="U18" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R18" s="13" t="e">
+      <c r="V18" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S18" s="13" t="e">
+      <c r="W18" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T18" s="13" t="e">
+      <c r="X18" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U18" s="13" t="e">
+      <c r="Y18" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V18" s="13" t="e">
+      <c r="Z18" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W18" s="13" t="e">
+      <c r="AA18" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X18" s="13" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y18" s="13" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z18" s="13" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA18" s="13" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="14">
+      <c r="A19" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="11">
         <f t="shared" ref="B19:AA19" si="4">B14/B15</f>
-        <v>1.9463989988422434</v>
-      </c>
-      <c r="C19" s="14">
+        <v>1.9639341249579394</v>
+      </c>
+      <c r="C19" s="11">
         <f t="shared" si="4"/>
-        <v>1.5969023152531543</v>
-      </c>
-      <c r="D19" s="14">
+        <v>1.7931318370427367</v>
+      </c>
+      <c r="D19" s="11">
         <f t="shared" si="4"/>
-        <v>2.1311951546146286</v>
-      </c>
-      <c r="E19" s="14">
+        <v>2.11343519499284</v>
+      </c>
+      <c r="E19" s="11">
         <f t="shared" si="4"/>
-        <v>2.5889544013334715</v>
-      </c>
-      <c r="F19" s="14">
+        <v>2.5346406726341679</v>
+      </c>
+      <c r="F19" s="11">
         <f t="shared" si="4"/>
         <v>2.4660378507620599</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="11">
         <f t="shared" si="4"/>
-        <v>2.2323631626940821</v>
-      </c>
-      <c r="H19" s="14">
+        <v>2.2708521827405317</v>
+      </c>
+      <c r="H19" s="11">
         <f t="shared" si="4"/>
         <v>2.4083499341573376</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="11">
         <f t="shared" si="4"/>
-        <v>3.0062368930240653</v>
-      </c>
-      <c r="J19" s="14">
+        <v>2.4978898848201432</v>
+      </c>
+      <c r="J19" s="11">
+        <f t="shared" si="4"/>
+        <v>2.3371524493548179</v>
+      </c>
+      <c r="K19" s="11">
+        <f t="shared" si="4"/>
+        <v>2.2733951871384526</v>
+      </c>
+      <c r="L19" s="11">
+        <f t="shared" si="4"/>
+        <v>2.3699619397918092</v>
+      </c>
+      <c r="M19" s="11">
+        <f t="shared" si="4"/>
+        <v>2.6246760566017802</v>
+      </c>
+      <c r="N19" s="11">
         <f t="shared" si="4"/>
         <v>2.8914509410747518</v>
       </c>
-      <c r="K19" s="14" t="e">
+      <c r="O19" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L19" s="14" t="e">
+        <v>2.6332007931007779</v>
+      </c>
+      <c r="P19" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M19" s="14" t="e">
+        <v>2.7912550855174882</v>
+      </c>
+      <c r="Q19" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N19" s="14" t="e">
+        <v>3.5370803962946189</v>
+      </c>
+      <c r="R19" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O19" s="14" t="e">
+        <v>3.7530667421305157</v>
+      </c>
+      <c r="S19" s="11" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P19" s="14" t="e">
+      <c r="T19" s="11" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q19" s="14" t="e">
+      <c r="U19" s="11" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R19" s="14" t="e">
+      <c r="V19" s="11" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S19" s="14" t="e">
+      <c r="W19" s="11" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T19" s="14" t="e">
+      <c r="X19" s="9" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U19" s="14" t="e">
+      <c r="Y19" s="9" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V19" s="14" t="e">
+      <c r="Z19" s="9" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W19" s="14" t="e">
+      <c r="AA19" s="9" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X19" s="12" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y19" s="12" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z19" s="12" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA19" s="12" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="14">
+      <c r="A20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="11">
         <f t="shared" ref="B20:AA20" si="5">B14/B21</f>
-        <v>13.217007883660232</v>
-      </c>
-      <c r="C20" s="14">
+        <v>13.336080026756271</v>
+      </c>
+      <c r="C20" s="11">
         <f t="shared" si="5"/>
-        <v>33.61806143212187</v>
-      </c>
-      <c r="D20" s="14">
+        <v>37.749094404713112</v>
+      </c>
+      <c r="D20" s="11">
         <f t="shared" si="5"/>
-        <v>7.0195847956048594</v>
-      </c>
-      <c r="E20" s="14">
+        <v>6.961088255641485</v>
+      </c>
+      <c r="E20" s="11">
         <f t="shared" si="5"/>
-        <v>11.162147585361957</v>
-      </c>
-      <c r="F20" s="14">
+        <v>10.927976656997721</v>
+      </c>
+      <c r="F20" s="11">
         <f t="shared" si="5"/>
         <v>14.531854183653101</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="11">
         <f t="shared" si="5"/>
-        <v>34.300332447012309</v>
-      </c>
-      <c r="H20" s="14">
+        <v>34.891717489202172</v>
+      </c>
+      <c r="H20" s="11">
         <f t="shared" si="5"/>
         <v>9.1737351140912811</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="11">
         <f t="shared" si="5"/>
-        <v>28.7466815628107</v>
-      </c>
-      <c r="J20" s="14">
+        <v>17.090919321345112</v>
+      </c>
+      <c r="J20" s="11">
+        <f t="shared" si="5"/>
+        <v>22.327017713268855</v>
+      </c>
+      <c r="K20" s="11">
+        <f t="shared" si="5"/>
+        <v>81.826167878110482</v>
+      </c>
+      <c r="L20" s="11">
+        <f t="shared" si="5"/>
+        <v>12.895249004194515</v>
+      </c>
+      <c r="M20" s="11">
+        <f t="shared" si="5"/>
+        <v>25.098064287530878</v>
+      </c>
+      <c r="N20" s="11">
         <f t="shared" si="5"/>
         <v>94.349451225309167</v>
       </c>
-      <c r="K20" s="14" t="e">
+      <c r="O20" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L20" s="14" t="e">
+        <v>112.63532222876152</v>
+      </c>
+      <c r="P20" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M20" s="14" t="e">
+        <v>10.60130034285952</v>
+      </c>
+      <c r="Q20" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N20" s="14" t="e">
+        <v>13.397705222817788</v>
+      </c>
+      <c r="R20" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O20" s="14" t="e">
+        <v>15.317422568897939</v>
+      </c>
+      <c r="S20" s="11" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P20" s="14" t="e">
+      <c r="T20" s="11" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q20" s="14" t="e">
+      <c r="U20" s="11" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R20" s="14" t="e">
+      <c r="V20" s="11" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S20" s="14" t="e">
+      <c r="W20" s="11" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T20" s="14" t="e">
+      <c r="X20" s="9" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U20" s="14" t="e">
+      <c r="Y20" s="9" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V20" s="14" t="e">
+      <c r="Z20" s="9" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W20" s="14" t="e">
+      <c r="AA20" s="9" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X20" s="12" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y20" s="12" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z20" s="12" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA20" s="12" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>65</v>
+      <c r="A21" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="B21" s="6">
         <f t="shared" ref="B21:AA21" si="6">B10/B13</f>
@@ -1963,43 +2127,43 @@
       </c>
       <c r="I21" s="6">
         <f t="shared" si="6"/>
-        <v>18.089044429834953</v>
+        <v>30.425513702505402</v>
       </c>
       <c r="J21" s="6">
         <f t="shared" si="6"/>
+        <v>20.781996322072459</v>
+      </c>
+      <c r="K21" s="6">
+        <f t="shared" si="6"/>
+        <v>5.4261370355433147</v>
+      </c>
+      <c r="L21" s="6">
+        <f t="shared" si="6"/>
+        <v>34.896573137410982</v>
+      </c>
+      <c r="M21" s="6">
+        <f t="shared" si="6"/>
+        <v>18.089044429834953</v>
+      </c>
+      <c r="N21" s="6">
+        <f t="shared" si="6"/>
         <v>4.896689848218946</v>
       </c>
-      <c r="K21" s="6" t="e">
+      <c r="O21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L21" s="6" t="e">
+        <v>4.0307071619853785</v>
+      </c>
+      <c r="P21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M21" s="6" t="e">
+        <v>44.334183996264883</v>
+      </c>
+      <c r="Q21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N21" s="6" t="e">
+        <v>43.290995760393002</v>
+      </c>
+      <c r="R21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O21" s="6" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P21" s="6" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q21" s="6" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R21" s="6" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>39.171080989715684</v>
       </c>
       <c r="S21" s="6" t="e">
         <f t="shared" si="6"/>
@@ -2021,174 +2185,541 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X21" s="12" t="e">
+      <c r="X21" s="9" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y21" s="12" t="e">
+      <c r="Y21" s="9" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z21" s="12" t="e">
+      <c r="Z21" s="9" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA21" s="12" t="e">
+      <c r="AA21" s="9" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="13">
+      <c r="A22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="10">
         <f t="shared" ref="B22:AA22" si="7">B7/B9</f>
         <v>0.71815825587811088</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="10">
         <f t="shared" si="7"/>
         <v>0.64296548999008429</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="10">
         <f t="shared" si="7"/>
         <v>0.65108679771641964</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="10">
         <f t="shared" si="7"/>
         <v>0.73600488588855351</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="10">
         <f t="shared" si="7"/>
         <v>0.79070192487031521</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="10">
         <f t="shared" si="7"/>
         <v>0.77667624522899548</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="10">
         <f t="shared" si="7"/>
         <v>0.80121049011285517</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="10">
+        <f t="shared" si="7"/>
+        <v>1.0363129394969457</v>
+      </c>
+      <c r="J22" s="10">
+        <f t="shared" si="7"/>
+        <v>1.1394402112803643</v>
+      </c>
+      <c r="K22" s="10">
+        <f t="shared" si="7"/>
+        <v>1.2818687315106154</v>
+      </c>
+      <c r="L22" s="10">
+        <f t="shared" si="7"/>
+        <v>1.2063593071498062</v>
+      </c>
+      <c r="M22" s="10">
         <f t="shared" si="7"/>
         <v>1.4274358619762304</v>
       </c>
-      <c r="J22" s="13">
+      <c r="N22" s="10">
         <f t="shared" si="7"/>
         <v>1.4999866971338565</v>
       </c>
-      <c r="K22" s="13" t="e">
+      <c r="O22" s="10">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L22" s="13" t="e">
+        <v>1.418281342984568</v>
+      </c>
+      <c r="P22" s="10">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M22" s="13" t="e">
+        <v>1.3965953804625195</v>
+      </c>
+      <c r="Q22" s="10">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N22" s="13" t="e">
+        <v>1.5563889399985844</v>
+      </c>
+      <c r="R22" s="10">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O22" s="13" t="e">
+        <v>1.4714271328229485</v>
+      </c>
+      <c r="S22" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P22" s="13" t="e">
+      <c r="T22" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q22" s="13" t="e">
+      <c r="U22" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R22" s="13" t="e">
+      <c r="V22" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S22" s="13" t="e">
+      <c r="W22" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T22" s="13" t="e">
+      <c r="X22" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U22" s="13" t="e">
+      <c r="Y22" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V22" s="13" t="e">
+      <c r="Z22" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W22" s="13" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X22" s="13" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y22" s="13" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z22" s="13" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA22" s="13" t="e">
+      <c r="AA22" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+    </row>
+    <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+    </row>
+    <row r="28" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+    </row>
+    <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+    </row>
+    <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+    </row>
+    <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+    </row>
+    <row r="32" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+    </row>
+    <row r="33" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+    </row>
+    <row r="34" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+    </row>
+    <row r="35" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+    </row>
+    <row r="37" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+    </row>
+    <row r="38" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+    </row>
+    <row r="39" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+    </row>
+    <row r="40" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+    </row>
+    <row r="41" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+    </row>
+    <row r="42" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="12"/>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="12"/>
+      <c r="R43" s="12"/>
+    </row>
+    <row r="44" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+      <c r="M44" s="12"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="12"/>
+      <c r="P44" s="12"/>
+      <c r="Q44" s="12"/>
+      <c r="R44" s="12"/>
+    </row>
+    <row r="45" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="12"/>
+      <c r="P45" s="12"/>
+      <c r="Q45" s="12"/>
+      <c r="R45" s="12"/>
+    </row>
+    <row r="46" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="12"/>
+      <c r="R46" s="12"/>
+    </row>
+    <row r="47" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="12"/>
+      <c r="P47" s="12"/>
+      <c r="Q47" s="12"/>
+      <c r="R47" s="12"/>
+    </row>
+    <row r="48" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="12"/>
+      <c r="P48" s="12"/>
+      <c r="Q48" s="12"/>
+      <c r="R48" s="12"/>
+    </row>
+    <row r="49" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="N49" s="12"/>
+      <c r="O49" s="12"/>
+      <c r="P49" s="12"/>
+      <c r="Q49" s="12"/>
+      <c r="R49" s="12"/>
+    </row>
+    <row r="50" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
+      <c r="M50" s="12"/>
+      <c r="N50" s="12"/>
+      <c r="O50" s="12"/>
+      <c r="P50" s="12"/>
+      <c r="Q50" s="12"/>
+      <c r="R50" s="12"/>
+    </row>
+    <row r="51" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+      <c r="M51" s="12"/>
+      <c r="N51" s="12"/>
+      <c r="O51" s="12"/>
+      <c r="P51" s="12"/>
+      <c r="Q51" s="12"/>
+      <c r="R51" s="12"/>
+    </row>
+    <row r="52" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="12"/>
+      <c r="N52" s="12"/>
+      <c r="O52" s="12"/>
+      <c r="P52" s="12"/>
+      <c r="Q52" s="12"/>
+      <c r="R52" s="12"/>
+    </row>
+    <row r="53" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3146,142 +3677,142 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1">
         <v>3734</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="C3" s="1">
         <v>6365</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3">
         <v>6267</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3">
         <v>5029</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3">
         <v>10794</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3">
         <v>3356</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3">
         <v>16348</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C9" s="3">
         <v>1528</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C10" s="3">
         <v>11009</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
